--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NEW_JERSEY_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NEW_JERSEY_2014.xlsx
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C200">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C205">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C643">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C704">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C709">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="B1091" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1091">
@@ -20724,7 +20724,7 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1132">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1256">
